--- a/output/北塩原村_意思決定支援ガイドライン第2版_MECE.xlsx
+++ b/output/北塩原村_意思決定支援ガイドライン第2版_MECE.xlsx
@@ -1141,7 +1141,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>移植8で正式引用に改め、S-12を研修の確認に書き換えた</t>
+          <t>移植8で正式引用に改め、Ｓ-12を研修の確認に書き換えた</t>
         </is>
       </c>
     </row>
